--- a/media/exports/reports/2026-09/cash-payroll.xlsx
+++ b/media/exports/reports/2026-09/cash-payroll.xlsx
@@ -12,7 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Cash_at_bank_30_Sep">'Report'!$B$8</definedName>
+    <definedName name="Wages_to_pay_in_October">'Report'!$B$9</definedName>
+    <definedName name="After_the_tightest_pay_run_15_Oct">'Report'!$B$10</definedName>
+    <definedName name="Lowest_point_next_13_weeks">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$95</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -71,12 +78,12 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="002F7A5D"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="0025342A"/>
+      <color rgb="002F7A5D"/>
     </font>
   </fonts>
   <fills count="3">
@@ -123,16 +130,18 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -216,6 +225,326 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>October: where the cash comes from and goes (forecast)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>October: where the cash comes from and goes (forecast)</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="#,##0;(#,##0)"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$15:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$15:$B$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Cash at bank by date</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Cash at bank</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$6:$A$96</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$E$6:$E$96</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="7"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2070000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="cash_payroll_Data" displayName="cash_payroll_Data" ref="A5:E96" headerRowCount="1">
+  <autoFilter ref="A5:E96"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Actual or forecast"/>
+    <tableColumn id="3" name="Money in"/>
+    <tableColumn id="4" name="Money out"/>
+    <tableColumn id="5" name="Cash at bank"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -531,14 +860,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -636,1120 +965,1128 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Cash at bank was $59,746 at 30 September. October has 3 pay runs ($113,400). The tightest is 15 October: $53,846 left after paying wages, $16,046 more than a pay run in reserve. The lowest point in the 13 weeks is ($343) on 30 November.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>October: where the cash comes from and goes (forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>October: where the cash comes from and goes (forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unpaid invoices collected</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>18 invoices ($8,963) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, 15 October would be $44,883. October is one of the two months a year with three pay runs: $37,800 more wages than a usual month. The PAYG instalment ($7,017) is due 28 October.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>New work collected</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>Workings!B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Wages (3 pay runs)</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>Workings!B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Suppliers and overheads</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>Workings!B78</f>
+        <v/>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>How this forecast has done so far</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>For 5 October it said $110,127; the bank says $47,244, $62,883 less. $64,300 of it is 7 invoices expected by then and not yet paid, the largest Wacol warehouse switchboard ($46,800). (Workings sheet: "From gross margin to profit".)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tax, interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>Workings!B84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21"/>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Cash at bank, every day: actual to 30 Sep, then forecast to 30 Dec: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>October: where the cash comes from and goes (forecast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>13 weeks, week by week</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Week ending</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Cash at start</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="B26" s="6">
-        <f>Workings!B64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="B27" s="6">
-        <f>Workings!B71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Wages (3 pay runs)</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
-        <f>Workings!B80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="B29" s="6">
-        <f>Workings!B89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Tax, interest and equipment finance</t>
-        </is>
-      </c>
-      <c r="B30" s="6">
-        <f>Workings!B95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Tax, interest and finance</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Cash at end</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Lowest in the week</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>7 Oct</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>$59,746</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>$94,563</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>$3,872</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>($37,800)</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>$120,381</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>$60,746</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>13 weeks, week by week</t>
+          <t>14 Oct</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>$120,381</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>$18,600</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>$6,454</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>$145,435</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>$121,672</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Week ending</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Cash at start</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Unpaid invoices collected</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>New work collected</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Wages</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Suppliers and overheads</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Tax, interest and finance</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Cash at end</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Lowest in the week</t>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>21 Oct</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>$145,435</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>$12,900</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>$6,454</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>($37,800)</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>($55,080)</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>$71,909</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>$53,846</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>7 Oct</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>$59,746</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>$94,563</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>$3,872</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>28 Oct</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>$71,909</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>$9,800</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>$6,454</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>($12,017)</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>$76,145</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>$73,199</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>4 Nov</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>$76,145</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>$15,200</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>$63,676</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>($37,800)</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>($55,080)</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>($1,080)</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>$61,062</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>$54,197</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>11 Nov</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>$61,062</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>$34,325</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>$120,381</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>$60,746</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>14 Oct</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>$120,381</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>$18,600</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>$6,454</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>$95,387</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>$67,927</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>18 Nov</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>$95,387</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>$145,435</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>$121,672</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>21 Oct</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>$145,435</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>$12,900</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>$6,454</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>$34,325</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>($37,800)</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>$71,909</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>$53,846</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>28 Oct</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>$71,909</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>$9,800</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>$6,454</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>$36,832</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>$29,967</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>25 Nov</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>$36,832</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>$34,325</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>($12,017)</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>$76,145</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>$73,199</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>4 Nov</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>$76,145</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>$15,200</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>$63,676</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>$71,157</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>$43,697</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2 Dec</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>$71,157</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>$74,825</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>($37,800)</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>($1,080)</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>$61,062</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>$54,197</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>11 Nov</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>$61,062</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>($6,080)</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>$47,022</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>($343)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>9 Dec</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>$47,022</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>$95,387</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>$67,927</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>18 Nov</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>$95,387</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>$81,346</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>$53,886</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>16 Dec</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>$81,346</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>($37,800)</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>$36,832</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>$29,967</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>25 Nov</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>$36,832</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>$22,791</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>$15,926</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>23 Dec</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>$22,791</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>$71,157</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>$43,697</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>2 Dec</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>$71,157</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>$57,116</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>$29,656</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>30 Dec</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>$57,116</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>$74,825</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>$34,325</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>($37,800)</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>($55,080)</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>($6,080)</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>$47,022</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>($343)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>9 Dec</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>$47,022</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>$81,346</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>$53,886</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>16 Dec</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>$81,346</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>($37,800)</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>($55,080)</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>$22,791</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>$15,926</t>
-        </is>
-      </c>
-    </row>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>($5,000)</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>$48,641</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>$26,181</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>23 Dec</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>$22,791</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>$57,116</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>$29,656</t>
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Invoices past the customer's usual payment date ($8,963)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>30 Dec</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>$57,116</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>($37,800)</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>($5,000)</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>$48,641</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>$26,181</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Customer or job</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Usually pays in (days)</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Days since invoiced</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 15, September</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>$775</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Invoices past the customer's usual payment date ($8,963)</t>
+          <t>Call-out 9, September</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>22 Sep</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>$762</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Customer or job</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Invoiced</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Usually pays in (days)</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Days since invoiced</t>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 40, September</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>1 Sep</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>$623</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 15, September</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 29, September</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>28 Sep</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>$606</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 32, September</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>21 Sep</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>$597</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 28, September</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>25 Sep</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>$563</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 49, September</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>27 Sep</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>$550</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 63, September</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>$775</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>$532</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 9, September</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>22 Sep</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>$762</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 11, September</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>24 Sep</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>$526</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 40, September</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>1 Sep</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>$623</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 50, September</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>28 Sep</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>$517</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 29, September</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>28 Sep</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>$606</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 32, September</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>21 Sep</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>$597</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 28, September</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>25 Sep</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>$563</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 49, September</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>27 Sep</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>$550</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 63, September</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>15 Sep</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>$532</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="57"/>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 11, September</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>24 Sep</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>$526</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>Call-out 50, September</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>28 Sep</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>$517</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>How this forecast has done so far</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>For 5 October it said $110,127; the bank says $47,244, $62,883 less. $64,300 of it is 7 invoices expected by then and not yet paid, the largest Wacol warehouse switchboard ($46,800). (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
     <row r="60"/>
-    <row r="61"/>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Cash at bank was $59,746 at 30 September. October has 3 pay runs ($113,400). The tightest is 15 October: $53,846 left after paying wages, $16,046 more than a pay run in reserve. The lowest point in the 13 weeks is ($343) on 30 November.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>18 invoices ($8,963) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, 15 October would be $44,883. October is one of the two months a year with three pay runs: $37,800 more wages than a usual month. The PAYG instalment ($7,017) is due 28 October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="31" min="0" max="16383" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="28" min="0" max="16383" man="1"/>
+    <brk id="60" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1778,14 +2115,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -2131,14 +2468,14 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Forecast made 30 September against the bank, 5 October</t>
+          <t>Unpaid invoices collected in October</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Actual cash − forecast cash</t>
+          <t>Each invoice unpaid at the start, on its customer's usual payment date</t>
         </is>
       </c>
     </row>
@@ -2146,300 +2483,300 @@
       <c r="A52" s="4" t="inlineStr"/>
       <c r="B52" s="5" t="inlineStr">
         <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Expected in the month</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>151063</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>36 invoices unpaid at 30 September; overdue ones assumed a week from then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>New work collected in October</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Contract fees (1st of the month, on each contract's terms) + installations and call-outs at the last three months' run rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>Expected in the month</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="n">
+        <v>73180</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Run rate from July, August, September.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>Pay runs in October</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Number of fortnightly pay runs × the last pay run</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Last pay run (17 September)</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>37800</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pay runs in October (1 Oct, 15 Oct, 29 Oct)</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>Wages paid in October</t>
+        </is>
+      </c>
+      <c r="B69" s="16">
+        <f>B67*B68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Wages include all on-costs. Fortnightly pay means two months a year have three pay runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Suppliers and overheads in October</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Last month's bills (trade creditors) + the month's overheads, paid on the 15th and at month end</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr"/>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Bills owed for September's materials and subcontractors</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>78060</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Overheads (at September's level)</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="n">
+        <v>32100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>Paid in the month</t>
+        </is>
+      </c>
+      <c r="B78" s="16">
+        <f>B76+B77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>Tax, interest and equipment finance in October</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Interest + equipment finance repayment (+ the PAYG instalment in Jan, Apr, Jul, Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr"/>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>Paid in the month</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="n">
+        <v>12017</v>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>Forecast made 30 September against the bank, 5 October</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Actual cash − forecast cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr"/>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
           <t>5 Oct</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Forecast for 5 October</t>
         </is>
       </c>
-      <c r="B53" s="14" t="n">
+      <c r="B90" s="14" t="n">
         <v>110127</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Actual, 5 October</t>
         </is>
       </c>
-      <c r="B54" s="14" t="n">
+      <c r="B91" s="14" t="n">
         <v>47244</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Actual − forecast</t>
         </is>
       </c>
-      <c r="B55" s="14">
-        <f>B54-B53</f>
+      <c r="B92" s="14">
+        <f>B91-B90</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Of which: invoices expected by then, not yet paid</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
+      <c r="B93" s="14" t="n">
         <v>-64300</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
         <is>
           <t>Everything else (timing of other money in and out)</t>
         </is>
       </c>
-      <c r="B57" s="16">
-        <f>B55-B56</f>
+      <c r="B94" s="16">
+        <f>B92-B93</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Not yet paid: Wacol warehouse switchboard $46,800; Milton office tower $4,200; Rocklea factory $3,900; Bulimba school $2,800; West End brewery $2,600….</t>
         </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Unpaid invoices collected in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>Each invoice unpaid at the start, on its customer's usual payment date</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
-        <is>
-          <t>Expected in the month</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="n">
-        <v>151063</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>36 invoices unpaid at 30 September; overdue ones assumed a week from then.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>New work collected in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>Contract fees (1st of the month, on each contract's terms) + installations and call-outs at the last three months' run rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="inlineStr">
-        <is>
-          <t>Expected in the month</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="n">
-        <v>73180</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Run rate from July, August, September.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
-        <is>
-          <t>Pay runs in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>Number of fortnightly pay runs × the last pay run</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Last pay run (17 September)</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="n">
-        <v>37800</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Pay runs in October (1 Oct, 15 Oct, 29 Oct)</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="15" t="inlineStr">
-        <is>
-          <t>Wages paid in October</t>
-        </is>
-      </c>
-      <c r="B80" s="16">
-        <f>B78*B79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Wages include all on-costs. Fortnightly pay means two months a year have three pay runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
-        <is>
-          <t>Suppliers and overheads in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>Last month's bills (trade creditors) + the month's overheads, paid on the 15th and at month end</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr"/>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Bills owed for September's materials and subcontractors</t>
-        </is>
-      </c>
-      <c r="B87" s="14" t="n">
-        <v>78060</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Overheads (at September's level)</t>
-        </is>
-      </c>
-      <c r="B88" s="14" t="n">
-        <v>32100</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>Paid in the month</t>
-        </is>
-      </c>
-      <c r="B89" s="16">
-        <f>B87+B88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="13" t="inlineStr">
-        <is>
-          <t>Tax, interest and equipment finance in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>Interest + equipment finance repayment (+ the PAYG instalment in Jan, Apr, Jul, Oct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr"/>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>Paid in the month</t>
-        </is>
-      </c>
-      <c r="B95" s="16" t="n">
-        <v>12017</v>
       </c>
     </row>
     <row r="96"/>
@@ -2451,7 +2788,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2460,7 +2797,7 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="23" min="0" max="16383" man="1"/>
     <brk id="49" min="0" max="16383" man="1"/>
-    <brk id="74" min="0" max="16383" man="1"/>
+    <brk id="80" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2491,14 +2828,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4784,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4458,5 +4795,9 @@
     <brk id="61" min="0" max="16383" man="1"/>
     <brk id="91" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-09/cash-payroll.xlsx
+++ b/media/exports/reports/2026-09/cash-payroll.xlsx
@@ -13,11 +13,11 @@
   </sheets>
   <definedNames>
     <definedName name="Cash_at_bank_30_Sep">'Report'!$B$8</definedName>
-    <definedName name="Wages_to_pay_in_October">'Report'!$B$9</definedName>
-    <definedName name="After_the_tightest_pay_run_15_Oct">'Report'!$B$10</definedName>
+    <definedName name="Paid_to_employees_in_October">'Report'!$B$9</definedName>
+    <definedName name="After_the_tightest_pay_run_29_Oct">'Report'!$B$10</definedName>
     <definedName name="Lowest_point_next_13_weeks">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$I$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$J$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$99</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$96</definedName>
   </definedNames>
@@ -323,6 +323,20 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <dLbls>
             <numFmt formatCode="#,##0;(#,##0)"/>
             <showLegendKey val="0"/>
@@ -333,12 +347,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$15:$A$19</f>
+              <f>'Report'!$A$15:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$15:$B$19</f>
+              <f>'Report'!$B$15:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -488,7 +502,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2070000"/>
+    <ext cx="5400000" cy="2340000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -836,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -848,6 +862,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,7 +882,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -875,7 +890,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>A 13-week cash forecast from 30 September: cash at bank, plus what customers owe on their usual payment dates and new work at its recent rate, less pay runs, supplier bills, tax and finance on their due dates. Every day opens its workings.</t>
+          <t>A 13-week cash forecast from 30 September: cash at bank, plus what customers owe on their usual payment dates and new work at its recent rate, less pay runs, supplier bills, the BAS and finance on their due dates. Every day opens its workings.</t>
         </is>
       </c>
     </row>
@@ -916,7 +931,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wages to pay in October</t>
+          <t>Paid to employees in October</t>
         </is>
       </c>
       <c r="B9" s="6">
@@ -925,23 +940,23 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>3 fortnightly pay runs</t>
+          <t>3 fortnightly pay runs, net pay + super</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>After the tightest pay run, 15 Oct</t>
+          <t>After the tightest pay run, 29 Oct</t>
         </is>
       </c>
       <c r="B10" s="6">
-        <f>Workings!B33</f>
+        <f>Workings!B34</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>buffer: one pay run, $37,800</t>
+          <t>buffer: one pay run, $36,611</t>
         </is>
       </c>
     </row>
@@ -952,7 +967,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>Workings!B46</f>
+        <f>Workings!B48</f>
         <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -984,7 +999,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>Workings!B53</f>
+        <f>Workings!B55</f>
         <v/>
       </c>
     </row>
@@ -995,18 +1010,18 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>Workings!B60</f>
+        <f>Workings!B62</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wages (3 pay runs)</t>
+          <t>Pay runs (3)</t>
         </is>
       </c>
       <c r="B17" s="6">
-        <f>Workings!B69</f>
+        <f>Workings!B71</f>
         <v/>
       </c>
     </row>
@@ -1017,213 +1032,136 @@
         </is>
       </c>
       <c r="B18" s="6">
-        <f>Workings!B78</f>
+        <f>Workings!B83</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tax, interest and equipment finance</t>
+          <t>BAS (GST and PAYG)</t>
         </is>
       </c>
       <c r="B19" s="6">
-        <f>Workings!B84</f>
+        <f>Workings!B92</f>
         <v/>
       </c>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+    </row>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Cash at bank, every day: actual to 30 Sep, then forecast to 30 Dec: every month is on the Data sheet.</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Cash at bank, every day: actual to 30 Sep, then forecast to 30 Dec: every month is on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>13 weeks, week by week</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Week ending</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Cash at start</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Wages</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Pay runs</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Tax, interest and finance</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>BAS (GST and PAYG)</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Interest and finance</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Cash at end</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Lowest in the week</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>7 Oct</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>$59,746</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>$94,563</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>$3,872</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>($37,800)</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>$120,381</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>$60,746</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>14 Oct</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>$120,381</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>$18,600</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>$6,454</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>$145,435</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>$121,672</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>21 Oct</t>
+          <t>7 Oct</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>$145,435</t>
+          <t>$120,228</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>$12,900</t>
+          <t>$116,158</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>$6,454</t>
+          <t>$3,129</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>($37,800)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -1233,34 +1171,39 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>$71,909</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>$53,846</t>
+          <t>$202,904</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>$132,057</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>28 Oct</t>
+          <t>14 Oct</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>$71,909</t>
+          <t>$202,904</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$22,880</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>$6,454</t>
+          <t>$6,259</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -1275,170 +1218,190 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>($12,017)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>$76,145</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>$73,199</t>
+          <t>$232,043</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>$202,904</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>4 Nov</t>
+          <t>21 Oct</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>$76,145</t>
+          <t>$232,043</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>$15,200</t>
+          <t>$15,840</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>$63,676</t>
+          <t>$7,824</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>($37,800)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>($1,080)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>$61,062</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>$54,197</t>
+          <t>$158,508</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>$134,844</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>11 Nov</t>
+          <t>28 Oct</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>$61,062</t>
+          <t>$158,508</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
+          <t>$12,100</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>$7,823</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>($86,253)</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>$95,387</t>
+          <t>($5,000)</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>$67,927</t>
+          <t>$87,178</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>$87,178</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>18 Nov</t>
+          <t>4 Nov</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>$95,387</t>
+          <t>$87,178</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
+          <t>$18,700</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>$71,657</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>($36,611)</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>($60,588)</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>($37,800)</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>($55,080)</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>$36,832</t>
+          <t>($1,080)</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>$29,967</t>
+          <t>$79,256</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>$69,267</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>25 Nov</t>
+          <t>11 Nov</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>$36,832</t>
+          <t>$79,256</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -1448,7 +1411,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$42,693</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -1468,24 +1431,29 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>$71,157</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>$43,697</t>
+          <t>$121,949</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>$86,230</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>2 Dec</t>
+          <t>18 Nov</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>$71,157</t>
+          <t>$121,949</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -1495,44 +1463,49 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>$74,825</t>
+          <t>$42,693</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>($37,800)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>($6,080)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>$47,022</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>($343)</t>
+          <t>$67,443</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>$58,905</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>9 Dec</t>
+          <t>25 Nov</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>$47,022</t>
+          <t>$67,443</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1542,7 +1515,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$42,694</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -1562,24 +1535,29 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>$81,346</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>$53,886</t>
+          <t>$110,137</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>$74,417</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>16 Dec</t>
+          <t>2 Dec</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>$81,346</t>
+          <t>$110,137</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -1589,17 +1567,17 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$92,578</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>($37,800)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -1609,24 +1587,29 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>$22,791</t>
+          <t>($6,080)</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>$15,926</t>
+          <t>$99,436</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>$41,013</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>23 Dec</t>
+          <t>9 Dec</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>$22,791</t>
+          <t>$99,436</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -1636,7 +1619,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$42,694</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -1656,435 +1639,668 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>$57,116</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>$29,656</t>
+          <t>$142,130</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>$106,410</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t>16 Dec</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>$142,130</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>$42,693</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>($36,611)</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>($60,588)</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>$87,624</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>$80,650</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>23 Dec</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>$87,624</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>$42,694</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>$130,318</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>$94,598</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
           <t>30 Dec</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>$57,116</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>$130,318</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>$34,325</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>($37,800)</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>$41,129</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>($36,611)</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>($5,000)</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>$48,641</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>$26,181</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Invoices past the customer's usual payment date ($8,963)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>$129,836</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>$100,681</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Invoices past the customer's usual payment date ($8,734): the forecast assumes these arrive within a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Customer or job</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Invoiced</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Amount (incl. GST)</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Usually pays in (days)</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Days since invoiced</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Call-out 15, September</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>15 Sep</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>$775</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Call-out 9, September</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>22 Sep</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>$762</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Call-out 40, September</t>
+          <t>Call-out 15, September</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>1 Sep</t>
+          <t>15 Sep</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>$623</t>
+          <t>$932</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Call-out 29, September</t>
+          <t>Call-out 9, September</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>28 Sep</t>
+          <t>22 Sep</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>$606</t>
+          <t>$917</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Call-out 32, September</t>
+          <t>Call-out 40, September</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>21 Sep</t>
+          <t>1 Sep</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>$597</t>
+          <t>$735</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Call-out 28, September</t>
+          <t>Call-out 32, September</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>25 Sep</t>
+          <t>21 Sep</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>$563</t>
+          <t>$706</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Call-out 49, September</t>
+          <t>Call-out 28, September</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>27 Sep</t>
+          <t>25 Sep</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>$550</t>
+          <t>$659</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Call-out 63, September</t>
+          <t>Call-out 11, September</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>15 Sep</t>
+          <t>24 Sep</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>$532</t>
+          <t>$638</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Call-out 11, September</t>
+          <t>Call-out 63, September</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>24 Sep</t>
+          <t>15 Sep</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>$526</t>
+          <t>$635</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Call-out 50, September</t>
+          <t>Call-out 21, September</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>28 Sep</t>
+          <t>25 Sep</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>$517</t>
+          <t>$567</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 22, September</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>17 Sep</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>$535</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>How this forecast has done so far</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>For 5 October it said $110,127; the bank says $47,244, $62,883 less. $64,300 of it is 7 invoices expected by then and not yet paid, the largest Wacol warehouse switchboard ($46,800). (Workings sheet: "From gross margin to profit".)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 38, September</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>23 Sep</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>$459</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 26, September</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>26 Sep</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>$441</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 20, September</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>24 Sep</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>$416</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 31, September</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>13 Sep</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>$416</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 61, September</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>19 Sep</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>$351</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 43, September</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>16 Sep</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>$327</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Cash at bank was $59,746 at 30 September. October has 3 pay runs ($113,400). The tightest is 15 October: $53,846 left after paying wages, $16,046 more than a pay run in reserve. The lowest point in the 13 weeks is ($343) on 30 November.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Cash at bank was $120,228 at 30 September. October has 3 pay runs ($109,833). The tightest is 29 October: $69,267 left after paying wages, $32,656 more than a pay run in reserve. The lowest point in the 13 weeks is $41,013 on 30 November.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>18 invoices ($8,963) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, 15 October would be $44,883. October is one of the two months a year with three pay runs: $37,800 more wages than a usual month. The PAYG instalment ($7,017) is due 28 October.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67"/>
+    <row r="69" ht="75" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>15 invoices ($8,734) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, the lowest point would be $32,279. October is one of the two months a year with three pay runs: $36,611 more than a usual month. The July to September BAS ($86,253) is due 28 October: GST $32,817, PAYG withheld $47,754 and the PAYG instalment $5,682.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="71"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
+    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A66:D66"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="28" min="0" max="16383" man="1"/>
-    <brk id="60" min="0" max="16383" man="1"/>
+    <brk id="30" min="0" max="16383" man="1"/>
+    <brk id="64" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2096,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2122,7 +2338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2382,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>337366</v>
+        <v>413536</v>
       </c>
     </row>
     <row r="10">
@@ -2176,7 +2392,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>-365620</v>
+        <v>-381308</v>
       </c>
     </row>
     <row r="11">
@@ -2209,7 +2425,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Number of fortnightly pay runs × the last pay run</t>
+          <t>Number of fortnightly pay runs × the cash each one takes</t>
         </is>
       </c>
     </row>
@@ -2224,11 +2440,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Last pay run (17 September)</t>
+          <t>Last pay run, net pay + super (17 September)</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>37800</v>
+        <v>36611</v>
       </c>
     </row>
     <row r="19">
@@ -2244,7 +2460,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Wages paid in October</t>
+          <t>Paid to employees and their super funds in October</t>
         </is>
       </c>
       <c r="B20" s="16">
@@ -2255,7 +2471,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Wages include all on-costs. Fortnightly pay means two months a year have three pay runs.</t>
+          <t>Each pay run is a 26th of the year's gross wages: net pay and super leave the bank on pay day, and the PAYG withheld goes to the ATO with the BAS. Fortnightly pay means two months a year have three pay runs.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2480,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Forecast cash at bank, 15 Oct 2026</t>
+          <t>Forecast cash at bank, 29 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2495,7 @@
       <c r="A26" s="4" t="inlineStr"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>15 Oct</t>
+          <t>29 Oct</t>
         </is>
       </c>
     </row>
@@ -2290,53 +2506,53 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>145434.9393939395</v>
+        <v>87178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unpaid invoices expected</t>
+          <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>0</v>
+        <v>18700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>New work expected to be paid</t>
+          <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>1290.742424242424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pay run</t>
+          <t>Pay run (net pay + super)</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Suppliers and overheads</t>
+          <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>-55080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tax, interest and equipment finance</t>
+          <t>BAS: GST, PAYG withheld and PAYG instalment</t>
         </is>
       </c>
       <c r="B32" s="14" t="n">
@@ -2344,71 +2560,71 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B33" s="16">
-        <f>B27+B28+B29+B30+B31+B32</f>
+      <c r="B34" s="16">
+        <f>B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Forecast.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Forecast cash at bank, 30 Nov 2026</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Yesterday's cash + money in − money out</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>30 Nov</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cash at bank, end of the day before</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n">
-        <v>60816.51515151527</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Unpaid invoices expected</t>
+          <t>Cash at bank, end of the day before</t>
         </is>
       </c>
       <c r="B41" s="14" t="n">
-        <v>0</v>
+        <v>89039</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>New work expected to be paid</t>
+          <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
       <c r="B42" s="14" t="n">
@@ -2418,377 +2634,417 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pay run</t>
+          <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
       <c r="B43" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Suppliers and overheads</t>
+          <t>Pay run (net pay + super)</t>
         </is>
       </c>
       <c r="B44" s="14" t="n">
-        <v>-55080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tax, interest and equipment finance</t>
+          <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
       <c r="B45" s="14" t="n">
+        <v>-60588</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BAS: GST, PAYG withheld and PAYG instalment</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
         <v>-6080</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B46" s="16">
-        <f>B40+B41+B42+B43+B44+B45</f>
+      <c r="B48" s="16">
+        <f>B41+B42+B43+B44+B45+B46+B47</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Forecast.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Unpaid invoices collected in October</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Each invoice unpaid at the start, on its customer's usual payment date</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Each invoice unpaid at the start, on its customer's usual payment date (next banking day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Expected in the month</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>151063</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Expected in the month (incl. GST)</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>185678</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>36 invoices unpaid at 30 September; overdue ones assumed a week from then.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>New work collected in October</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Contract fees (1st of the month, on each contract's terms) + installations and call-outs at the last three months' run rate</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr"/>
-      <c r="B59" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Expected in the month</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="n">
-        <v>73180</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Run rate from July, August, September.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Expected in the month (incl. GST)</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="n">
+        <v>26600</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Run rate from July, August, September. Every day's amount is in whole dollars, so the days add up to this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Pay runs in October</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>Number of fortnightly pay runs × the last pay run</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr"/>
-      <c r="B66" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Number of fortnightly pay runs × the cash each one takes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr"/>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Last pay run (17 September)</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="n">
-        <v>37800</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Last pay run, net pay + super (17 September)</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>36611</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Pay runs in October (1 Oct, 15 Oct, 29 Oct)</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
+      <c r="B70" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="15" t="inlineStr">
-        <is>
-          <t>Wages paid in October</t>
-        </is>
-      </c>
-      <c r="B69" s="16">
-        <f>B67*B68</f>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>Paid to employees and their super funds in October</t>
+        </is>
+      </c>
+      <c r="B71" s="16">
+        <f>B69*B70</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Wages include all on-costs. Fortnightly pay means two months a year have three pay runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="13" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Each pay run is a 26th of the year's gross wages: net pay and super leave the bank on pay day, and the PAYG withheld goes to the ATO with the BAS. Fortnightly pay means two months a year have three pay runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Suppliers and overheads in October</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>Last month's bills (trade creditors) + the month's overheads, paid on the 15th and at month end</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr"/>
-      <c r="B75" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Last month's bills (trade creditors) + the month's overheads, half on the 15th and half at month end, on banking days</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr"/>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Bills owed for September's materials and subcontractors</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="n">
-        <v>78060</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Overheads (at September's level)</t>
-        </is>
-      </c>
-      <c r="B77" s="14" t="n">
-        <v>32100</v>
-      </c>
-    </row>
     <row r="78">
-      <c r="A78" s="15" t="inlineStr">
-        <is>
-          <t>Paid in the month</t>
-        </is>
-      </c>
-      <c r="B78" s="16">
-        <f>B76+B77</f>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>September's bills for materials and subcontractors, incl. GST</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>85866</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Overheads, incl. GST (at September's level)</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>35310</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>October's supplier bills</t>
+        </is>
+      </c>
+      <c r="B80" s="14">
+        <f>B78+B79</f>
         <v/>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>Tax, interest and equipment finance in October</t>
-        </is>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>October run due 15 October: paid in October</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="n">
+        <v>-60588</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>Interest + equipment finance repayment (+ the PAYG instalment in Jan, Apr, Jul, Oct)</t>
-        </is>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>October run due 31 October, lands Mon 2 Nov (31 Oct isn't a banking day): paid in November, not October</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr"/>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>Paid in October</t>
+        </is>
+      </c>
+      <c r="B83" s="16">
+        <f>B81+B82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>BAS in October</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>GST on sales − GST credits + PAYG withheld + PAYG instalment, for the quarter, due on the 28th (quarterly, self-lodged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr"/>
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="15" t="inlineStr">
-        <is>
-          <t>Paid in the month</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="n">
-        <v>12017</v>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>Forecast made 30 September against the bank, 5 October</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>Actual cash − forecast cash</t>
-        </is>
-      </c>
-    </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr"/>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>5 Oct</t>
-        </is>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GST on sales less GST credits, July to September</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="n">
+        <v>-32817</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Forecast for 5 October</t>
+          <t>PAYG withheld from pay runs, July to September</t>
         </is>
       </c>
       <c r="B90" s="14" t="n">
-        <v>110127</v>
+        <v>-47754</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Actual, 5 October</t>
+          <t>PAYG income tax instalment, July to September</t>
         </is>
       </c>
       <c r="B91" s="14" t="n">
-        <v>47244</v>
+        <v>-5682</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Actual − forecast</t>
-        </is>
-      </c>
-      <c r="B92" s="14">
-        <f>B91-B90</f>
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>BAS paid in October</t>
+        </is>
+      </c>
+      <c r="B92" s="16">
+        <f>B89+B90+B91</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Of which: invoices expected by then, not yet paid</t>
-        </is>
-      </c>
-      <c r="B93" s="14" t="n">
-        <v>-64300</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>Everything else (timing of other money in and out)</t>
-        </is>
-      </c>
-      <c r="B94" s="16">
-        <f>B92-B93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Not yet paid: Wacol warehouse switchboard $46,800; Milton office tower $4,200; Rocklea factory $3,900; Bulimba school $2,800; West End brewery $2,600….</t>
-        </is>
-      </c>
-    </row>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>From the balance sheet at the quarter end: GST payable and PAYG withholding payable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance in October</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Interest at month end + the equipment finance repayment on the 28th (no GST on either)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr"/>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Paid in the month</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2796,8 +3052,8 @@
   </headerFooter>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="23" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
-    <brk id="80" min="0" max="16383" man="1"/>
+    <brk id="51" min="0" max="16383" man="1"/>
+    <brk id="74" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2835,7 +3091,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2879,13 +3135,13 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>38800</v>
+        <v>48440</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>60746</v>
+        <v>132057</v>
       </c>
     </row>
     <row r="7">
@@ -2900,13 +3156,13 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>60746</v>
+        <v>133401</v>
       </c>
     </row>
     <row r="8">
@@ -2921,13 +3177,13 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>62037</v>
+        <v>133401</v>
       </c>
     </row>
     <row r="9">
@@ -2942,13 +3198,13 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>48091</v>
+        <v>0</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>110127</v>
+        <v>133401</v>
       </c>
     </row>
     <row r="10">
@@ -2969,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>110127</v>
+        <v>133401</v>
       </c>
     </row>
     <row r="11">
@@ -2984,13 +3240,13 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>0</v>
+        <v>60769</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>110127</v>
+        <v>194170</v>
       </c>
     </row>
     <row r="12">
@@ -3005,13 +3261,13 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>10254</v>
+        <v>8734</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>120381</v>
+        <v>202904</v>
       </c>
     </row>
     <row r="13">
@@ -3026,13 +3282,13 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>121672</v>
+        <v>202904</v>
       </c>
     </row>
     <row r="14">
@@ -3047,13 +3303,13 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>19891</v>
+        <v>22880</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>141563</v>
+        <v>225784</v>
       </c>
     </row>
     <row r="15">
@@ -3068,13 +3324,13 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>142853</v>
+        <v>225784</v>
       </c>
     </row>
     <row r="16">
@@ -3089,13 +3345,13 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>144144</v>
+        <v>225784</v>
       </c>
     </row>
     <row r="17">
@@ -3110,13 +3366,13 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>0</v>
+        <v>4694</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>144144</v>
+        <v>230478</v>
       </c>
     </row>
     <row r="18">
@@ -3131,13 +3387,13 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>144144</v>
+        <v>232043</v>
       </c>
     </row>
     <row r="19">
@@ -3152,13 +3408,13 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>145435</v>
+        <v>232043</v>
       </c>
     </row>
     <row r="20">
@@ -3173,13 +3429,13 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>-92880</v>
+        <v>-97199</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>53846</v>
+        <v>134844</v>
       </c>
     </row>
     <row r="21">
@@ -3194,13 +3450,13 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>55136</v>
+        <v>136409</v>
       </c>
     </row>
     <row r="22">
@@ -3215,13 +3471,13 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>56427</v>
+        <v>136409</v>
       </c>
     </row>
     <row r="23">
@@ -3236,13 +3492,13 @@
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>14191</v>
+        <v>0</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>70618</v>
+        <v>136409</v>
       </c>
     </row>
     <row r="24">
@@ -3257,13 +3513,13 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>0</v>
+        <v>20534</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>70618</v>
+        <v>156943</v>
       </c>
     </row>
     <row r="25">
@@ -3278,13 +3534,13 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>70618</v>
+        <v>158508</v>
       </c>
     </row>
     <row r="26">
@@ -3299,13 +3555,13 @@
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>71909</v>
+        <v>158508</v>
       </c>
     </row>
     <row r="27">
@@ -3320,13 +3576,13 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>73199</v>
+        <v>158508</v>
       </c>
     </row>
     <row r="28">
@@ -3341,13 +3597,13 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>11091</v>
+        <v>13664</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>84290</v>
+        <v>172172</v>
       </c>
     </row>
     <row r="29">
@@ -3362,13 +3618,13 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>85581</v>
+        <v>172172</v>
       </c>
     </row>
     <row r="30">
@@ -3383,13 +3639,13 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>86872</v>
+        <v>172172</v>
       </c>
     </row>
     <row r="31">
@@ -3404,13 +3660,13 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>0</v>
+        <v>4694</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>86872</v>
+        <v>176866</v>
       </c>
     </row>
     <row r="32">
@@ -3425,13 +3681,13 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>86872</v>
+        <v>178431</v>
       </c>
     </row>
     <row r="33">
@@ -3446,13 +3702,13 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>-12017</v>
+        <v>-91253</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>76145</v>
+        <v>87178</v>
       </c>
     </row>
     <row r="34">
@@ -3467,13 +3723,13 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>16491</v>
+        <v>18700</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>54836</v>
+        <v>69267</v>
       </c>
     </row>
     <row r="35">
@@ -3488,13 +3744,13 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>56127</v>
+        <v>70832</v>
       </c>
     </row>
     <row r="36">
@@ -3509,13 +3765,13 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>47365</v>
+        <v>0</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>103492</v>
+        <v>70832</v>
       </c>
     </row>
     <row r="37">
@@ -3530,13 +3786,13 @@
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>110357</v>
+        <v>70832</v>
       </c>
     </row>
     <row r="38">
@@ -3551,13 +3807,13 @@
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>0</v>
+        <v>68527</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>-56160</v>
+        <v>-61668</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>54197</v>
+        <v>77691</v>
       </c>
     </row>
     <row r="39">
@@ -3572,13 +3828,13 @@
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>54197</v>
+        <v>79256</v>
       </c>
     </row>
     <row r="40">
@@ -3593,13 +3849,13 @@
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>61062</v>
+        <v>79256</v>
       </c>
     </row>
     <row r="41">
@@ -3614,13 +3870,13 @@
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>67927</v>
+        <v>86230</v>
       </c>
     </row>
     <row r="42">
@@ -3635,13 +3891,13 @@
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>74792</v>
+        <v>94768</v>
       </c>
     </row>
     <row r="43">
@@ -3656,13 +3912,13 @@
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>81657</v>
+        <v>94768</v>
       </c>
     </row>
     <row r="44">
@@ -3677,13 +3933,13 @@
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>88522</v>
+        <v>94768</v>
       </c>
     </row>
     <row r="45">
@@ -3698,13 +3954,13 @@
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>88522</v>
+        <v>113410</v>
       </c>
     </row>
     <row r="46">
@@ -3719,13 +3975,13 @@
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>88522</v>
+        <v>114975</v>
       </c>
     </row>
     <row r="47">
@@ -3740,13 +3996,13 @@
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>95387</v>
+        <v>121949</v>
       </c>
     </row>
     <row r="48">
@@ -3761,13 +4017,13 @@
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>64452</v>
+        <v>92312</v>
       </c>
     </row>
     <row r="49">
@@ -3782,13 +4038,13 @@
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>71317</v>
+        <v>100851</v>
       </c>
     </row>
     <row r="50">
@@ -3803,13 +4059,13 @@
         </is>
       </c>
       <c r="C50" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>78182</v>
+        <v>100851</v>
       </c>
     </row>
     <row r="51">
@@ -3824,13 +4080,13 @@
         </is>
       </c>
       <c r="C51" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>85047</v>
+        <v>100851</v>
       </c>
     </row>
     <row r="52">
@@ -3845,13 +4101,13 @@
         </is>
       </c>
       <c r="C52" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>-55080</v>
+        <v>-60588</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>29967</v>
+        <v>58905</v>
       </c>
     </row>
     <row r="53">
@@ -3866,13 +4122,13 @@
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>0</v>
+        <v>1564</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>29967</v>
+        <v>60469</v>
       </c>
     </row>
     <row r="54">
@@ -3887,13 +4143,13 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>36832</v>
+        <v>67443</v>
       </c>
     </row>
     <row r="55">
@@ -3908,13 +4164,13 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>43697</v>
+        <v>74417</v>
       </c>
     </row>
     <row r="56">
@@ -3929,13 +4185,13 @@
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>50562</v>
+        <v>82956</v>
       </c>
     </row>
     <row r="57">
@@ -3950,13 +4206,13 @@
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>57427</v>
+        <v>82956</v>
       </c>
     </row>
     <row r="58">
@@ -3971,13 +4227,13 @@
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>64292</v>
+        <v>82956</v>
       </c>
     </row>
     <row r="59">
@@ -3992,13 +4248,13 @@
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>64292</v>
+        <v>101598</v>
       </c>
     </row>
     <row r="60">
@@ -4013,13 +4269,13 @@
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D60" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>64292</v>
+        <v>103163</v>
       </c>
     </row>
     <row r="61">
@@ -4034,13 +4290,13 @@
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>71157</v>
+        <v>110137</v>
       </c>
     </row>
     <row r="62">
@@ -4055,13 +4311,13 @@
         </is>
       </c>
       <c r="C62" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>40222</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="63">
@@ -4076,13 +4332,13 @@
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>47087</v>
+        <v>89039</v>
       </c>
     </row>
     <row r="64">
@@ -4097,13 +4353,13 @@
         </is>
       </c>
       <c r="C64" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>53952</v>
+        <v>89039</v>
       </c>
     </row>
     <row r="65">
@@ -4118,13 +4374,13 @@
         </is>
       </c>
       <c r="C65" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>60817</v>
+        <v>89039</v>
       </c>
     </row>
     <row r="66">
@@ -4139,13 +4395,13 @@
         </is>
       </c>
       <c r="C66" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D66" s="14" t="n">
-        <v>-61160</v>
+        <v>-66668</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>-343</v>
+        <v>41013</v>
       </c>
     </row>
     <row r="67">
@@ -4160,13 +4416,13 @@
         </is>
       </c>
       <c r="C67" s="14" t="n">
-        <v>40500</v>
+        <v>51449</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>40157</v>
+        <v>92462</v>
       </c>
     </row>
     <row r="68">
@@ -4181,13 +4437,13 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>47022</v>
+        <v>99436</v>
       </c>
     </row>
     <row r="69">
@@ -4202,13 +4458,13 @@
         </is>
       </c>
       <c r="C69" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>53886</v>
+        <v>106410</v>
       </c>
     </row>
     <row r="70">
@@ -4223,13 +4479,13 @@
         </is>
       </c>
       <c r="C70" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D70" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>60751</v>
+        <v>114949</v>
       </c>
     </row>
     <row r="71">
@@ -4244,13 +4500,13 @@
         </is>
       </c>
       <c r="C71" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>67616</v>
+        <v>114949</v>
       </c>
     </row>
     <row r="72">
@@ -4265,13 +4521,13 @@
         </is>
       </c>
       <c r="C72" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>74481</v>
+        <v>114949</v>
       </c>
     </row>
     <row r="73">
@@ -4286,13 +4542,13 @@
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>74481</v>
+        <v>133591</v>
       </c>
     </row>
     <row r="74">
@@ -4307,13 +4563,13 @@
         </is>
       </c>
       <c r="C74" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>74481</v>
+        <v>135156</v>
       </c>
     </row>
     <row r="75">
@@ -4328,13 +4584,13 @@
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D75" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>81346</v>
+        <v>142130</v>
       </c>
     </row>
     <row r="76">
@@ -4349,13 +4605,13 @@
         </is>
       </c>
       <c r="C76" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>50411</v>
+        <v>112493</v>
       </c>
     </row>
     <row r="77">
@@ -4370,13 +4626,13 @@
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>57276</v>
+        <v>121032</v>
       </c>
     </row>
     <row r="78">
@@ -4391,13 +4647,13 @@
         </is>
       </c>
       <c r="C78" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>64141</v>
+        <v>121032</v>
       </c>
     </row>
     <row r="79">
@@ -4412,13 +4668,13 @@
         </is>
       </c>
       <c r="C79" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>71006</v>
+        <v>121032</v>
       </c>
     </row>
     <row r="80">
@@ -4433,13 +4689,13 @@
         </is>
       </c>
       <c r="C80" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>71006</v>
+        <v>139674</v>
       </c>
     </row>
     <row r="81">
@@ -4454,13 +4710,13 @@
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>0</v>
+        <v>1564</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>-55080</v>
+        <v>-60588</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>15926</v>
+        <v>80650</v>
       </c>
     </row>
     <row r="82">
@@ -4475,13 +4731,13 @@
         </is>
       </c>
       <c r="C82" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>22791</v>
+        <v>87624</v>
       </c>
     </row>
     <row r="83">
@@ -4496,13 +4752,13 @@
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>29656</v>
+        <v>94598</v>
       </c>
     </row>
     <row r="84">
@@ -4517,13 +4773,13 @@
         </is>
       </c>
       <c r="C84" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D84" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>36521</v>
+        <v>103137</v>
       </c>
     </row>
     <row r="85">
@@ -4538,13 +4794,13 @@
         </is>
       </c>
       <c r="C85" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>43386</v>
+        <v>103137</v>
       </c>
     </row>
     <row r="86">
@@ -4559,13 +4815,13 @@
         </is>
       </c>
       <c r="C86" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>50251</v>
+        <v>103137</v>
       </c>
     </row>
     <row r="87">
@@ -4580,13 +4836,13 @@
         </is>
       </c>
       <c r="C87" s="14" t="n">
-        <v>0</v>
+        <v>18642</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>50251</v>
+        <v>121779</v>
       </c>
     </row>
     <row r="88">
@@ -4601,13 +4857,13 @@
         </is>
       </c>
       <c r="C88" s="14" t="n">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="D88" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>50251</v>
+        <v>123344</v>
       </c>
     </row>
     <row r="89">
@@ -4622,13 +4878,13 @@
         </is>
       </c>
       <c r="C89" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D89" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>57116</v>
+        <v>130318</v>
       </c>
     </row>
     <row r="90">
@@ -4643,13 +4899,13 @@
         </is>
       </c>
       <c r="C90" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>-37800</v>
+        <v>-36611</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>26181</v>
+        <v>100681</v>
       </c>
     </row>
     <row r="91">
@@ -4664,13 +4920,13 @@
         </is>
       </c>
       <c r="C91" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D91" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>33046</v>
+        <v>100681</v>
       </c>
     </row>
     <row r="92">
@@ -4685,13 +4941,13 @@
         </is>
       </c>
       <c r="C92" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>39911</v>
+        <v>100681</v>
       </c>
     </row>
     <row r="93">
@@ -4706,13 +4962,13 @@
         </is>
       </c>
       <c r="C93" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>46776</v>
+        <v>100681</v>
       </c>
     </row>
     <row r="94">
@@ -4730,10 +4986,10 @@
         <v>0</v>
       </c>
       <c r="D94" s="14" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>41776</v>
+        <v>100681</v>
       </c>
     </row>
     <row r="95">
@@ -4748,13 +5004,13 @@
         </is>
       </c>
       <c r="C95" s="14" t="n">
-        <v>0</v>
+        <v>27181</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>41776</v>
+        <v>122862</v>
       </c>
     </row>
     <row r="96">
@@ -4769,13 +5025,13 @@
         </is>
       </c>
       <c r="C96" s="14" t="n">
-        <v>6865</v>
+        <v>6974</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>48641</v>
+        <v>129836</v>
       </c>
     </row>
   </sheetData>
@@ -4784,7 +5040,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-09/cash-payroll.xlsx
+++ b/media/exports/reports/2026-09/cash-payroll.xlsx
@@ -882,7 +882,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Call-out 15, September</t>
+          <t>Call-out CO-49240</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Call-out 9, September</t>
+          <t>Call-out CO-49233</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -1901,7 +1901,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Call-out 40, September</t>
+          <t>Call-out CO-49269</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Call-out 32, September</t>
+          <t>Call-out CO-49260</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Call-out 28, September</t>
+          <t>Call-out CO-49255</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -1982,7 +1982,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Call-out 11, September</t>
+          <t>Call-out CO-49235</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -2009,7 +2009,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Call-out 63, September</t>
+          <t>Call-out CO-49296</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -2036,7 +2036,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Call-out 21, September</t>
+          <t>Call-out CO-49247</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -2063,7 +2063,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Call-out 22, September</t>
+          <t>Call-out CO-49248</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -2090,7 +2090,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Call-out 38, September</t>
+          <t>Call-out CO-49267</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Call-out 26, September</t>
+          <t>Call-out CO-49253</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -2144,7 +2144,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Call-out 20, September</t>
+          <t>Call-out CO-49246</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Call-out 31, September</t>
+          <t>Call-out CO-49259</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Call-out 61, September</t>
+          <t>Call-out CO-49294</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -2225,7 +2225,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Call-out 43, September</t>
+          <t>Call-out CO-49273</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -2292,7 +2292,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2338,7 +2338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3091,7 +3091,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-09/cash-payroll.xlsx
+++ b/media/exports/reports/2026-09/cash-payroll.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Cash_at_bank_30_Sep">'Report'!$B$8</definedName>
-    <definedName name="Paid_to_employees_in_October">'Report'!$B$9</definedName>
-    <definedName name="After_the_tightest_pay_run_29_Oct">'Report'!$B$10</definedName>
-    <definedName name="Lowest_point_next_13_weeks">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$J$69</definedName>
+    <definedName name="Cash_at_bank_30_Sep">'Report'!$B$9</definedName>
+    <definedName name="Paid_to_employees_in_October">'Report'!$B$10</definedName>
+    <definedName name="After_the_tightest_pay_run_29_Oct">'Report'!$B$11</definedName>
+    <definedName name="Lowest_point_next_13_weeks">'Report'!$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$J$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$99</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$96</definedName>
@@ -54,6 +54,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -74,11 +79,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -116,25 +116,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -142,12 +145,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -347,12 +350,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$15:$A$20</f>
+              <f>'Report'!$A$16:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$15:$B$20</f>
+              <f>'Report'!$B$16:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -499,7 +502,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2340000"/>
@@ -850,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -882,7 +885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -890,175 +893,179 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Yes: $69,267 forecast in the bank after the 29 October pay run, the tightest in October, and at least one pay run in reserve for all 13 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>A 13-week cash forecast from 30 September: cash at bank, plus what customers owe on their usual payment dates and new work at its recent rate, less pay runs, supplier bills, the BAS and finance on their due dates. Every day opens its workings.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Cash at bank, 30 Sep</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B9" s="7">
         <f>Workings!B11</f>
         <v/>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>end of the day</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Paid to employees in October</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B10" s="7">
         <f>Workings!B20</f>
         <v/>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>3 fortnightly pay runs, net pay + super</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>After the tightest pay run, 29 Oct</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="7">
         <f>Workings!B34</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>buffer: one pay run, $36,611</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Lowest point, next 13 weeks</t>
         </is>
       </c>
-      <c r="B11" s="6">
+      <c r="B12" s="7">
         <f>Workings!B48</f>
         <v/>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>30 November</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>October: where the cash comes from and goes (forecast)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>October: where the cash comes from and goes (forecast)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B16" s="7">
         <f>Workings!B55</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B17" s="7">
         <f>Workings!B62</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pay runs (3)</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <f>Workings!B71</f>
-        <v/>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Pay runs (3)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>-109833</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B19" s="7">
         <f>Workings!B83</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>BAS (GST and PAYG)</t>
         </is>
       </c>
-      <c r="B19" s="6">
+      <c r="B20" s="7">
         <f>Workings!B92</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Interest and equipment finance</t>
         </is>
       </c>
-      <c r="B20" s="6">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="B21" s="7" t="n">
+        <v>-5000</v>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -1066,1241 +1073,1243 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Cash at bank, every day: actual to 30 Sep, then forecast to 30 Dec: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>13 weeks, week by week</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Week ending</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Cash at start</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Pay runs</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>BAS (GST and PAYG)</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Interest and finance</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>Cash at end</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>Lowest in the week</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>7 Oct</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>$120,228</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>$116,158</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>$3,129</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>$202,904</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>$132,057</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>14 Oct</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>$202,904</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>$22,880</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>$6,259</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>$232,043</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>$202,904</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>21 Oct</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>$232,043</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>$15,840</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>$7,824</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>$158,508</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>$134,844</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>28 Oct</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>$158,508</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>$12,100</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>$7,823</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>($86,253)</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>($5,000)</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>$87,178</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>$87,178</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>4 Nov</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>$87,178</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>$18,700</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>$71,657</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>($1,080)</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>$79,256</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>$69,267</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>11 Nov</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>$79,256</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>$42,693</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>$121,949</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>$86,230</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>18 Nov</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>$121,949</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>$42,693</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>$67,443</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>$58,905</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>25 Nov</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>$67,443</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>$42,694</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>$110,137</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>$74,417</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>2 Dec</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>$110,137</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>$92,578</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>($6,080)</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>$99,436</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>$41,013</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>9 Dec</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>$99,436</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>$42,694</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>$142,130</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>$106,410</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>16 Dec</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>$142,130</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>$42,693</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>$87,624</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>$80,650</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>23 Dec</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>$87,624</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>$42,694</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>$130,318</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>$94,598</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>30 Dec</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>$130,318</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>$41,129</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>($5,000)</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>$129,836</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>$100,681</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Invoices past the customer's usual payment date ($8,734): the forecast assumes these arrive within a week</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Customer or job</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Invoiced</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Amount (incl. GST)</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Usually pays in (days)</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Days since invoiced</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49240</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>$932</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49233</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>22 Sep</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>$917</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49269</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>$735</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49260</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>$706</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49255</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>25 Sep</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>$659</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49235</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>24 Sep</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>$638</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49296</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>$635</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49247</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>25 Sep</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>$567</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49248</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>17 Sep</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>$535</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49267</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>23 Sep</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>$459</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49253</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>26 Sep</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>$441</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49246</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>24 Sep</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>$416</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49259</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>13 Sep</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
         <is>
           <t>$416</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49294</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>19 Sep</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>$351</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49273</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>16 Sep</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>$327</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Cash at bank was $120,228 at 30 September. October has 3 pay runs ($109,833). The tightest is 29 October: $69,267 left after paying wages, $32,656 more than a pay run in reserve. The lowest point in the 13 weeks is $41,013 on 30 November.</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="75" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="70" ht="75" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>15 invoices ($8,734) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, the lowest point would be $32,279. October is one of the two months a year with three pay runs: $36,611 more than a usual month. The July to September BAS ($86,253) is due 28 October: GST $32,817, PAYG withheld $47,754 and the PAYG instalment $5,682.</t>
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71"/>
+    <row r="72"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A69:D69"/>
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="64" min="0" max="16383" man="1"/>
+    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="65" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2338,28 +2347,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Cash at bank, 30 September</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Opening balance + every day's money in − money out</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>30 Sep</t>
         </is>
@@ -2371,7 +2380,7 @@
           <t>Cash at bank, 31 July (opening balance)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>88000</v>
       </c>
     </row>
@@ -2381,7 +2390,7 @@
           <t>Money in, 1 August to 30 September</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>413536</v>
       </c>
     </row>
@@ -2391,17 +2400,17 @@
           <t>Money out, 1 August to 30 September</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>-381308</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="17">
         <f>B8+B9+B10</f>
         <v/>
       </c>
@@ -2416,22 +2425,22 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Pay runs in October</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Number of fortnightly pay runs × the cash each one takes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
@@ -2443,7 +2452,7 @@
           <t>Last pay run, net pay + super (17 September)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="15" t="n">
         <v>36611</v>
       </c>
     </row>
@@ -2453,17 +2462,17 @@
           <t>Pay runs in October (1 Oct, 15 Oct, 29 Oct)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Paid to employees and their super funds in October</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <f>B18*B19</f>
         <v/>
       </c>
@@ -2478,22 +2487,22 @@
     <row r="22"/>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Forecast cash at bank, 29 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Yesterday's cash + money in − money out</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>29 Oct</t>
         </is>
@@ -2505,7 +2514,7 @@
           <t>Cash at bank, end of the day before</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <v>87178</v>
       </c>
     </row>
@@ -2515,7 +2524,7 @@
           <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <v>18700</v>
       </c>
     </row>
@@ -2525,7 +2534,7 @@
           <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2535,7 +2544,7 @@
           <t>Pay run (net pay + super)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>-36611</v>
       </c>
     </row>
@@ -2545,7 +2554,7 @@
           <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2555,7 +2564,7 @@
           <t>BAS: GST, PAYG withheld and PAYG instalment</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2565,17 +2574,17 @@
           <t>Interest and equipment finance</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <f>B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
@@ -2590,22 +2599,22 @@
     <row r="36"/>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Forecast cash at bank, 30 Nov 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Yesterday's cash + money in − money out</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>30 Nov</t>
         </is>
@@ -2617,7 +2626,7 @@
           <t>Cash at bank, end of the day before</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
+      <c r="B41" s="15" t="n">
         <v>89039</v>
       </c>
     </row>
@@ -2627,7 +2636,7 @@
           <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2637,7 +2646,7 @@
           <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="15" t="n">
         <v>18642</v>
       </c>
     </row>
@@ -2647,7 +2656,7 @@
           <t>Pay run (net pay + super)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2657,7 +2666,7 @@
           <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="15" t="n">
         <v>-60588</v>
       </c>
     </row>
@@ -2667,7 +2676,7 @@
           <t>BAS: GST, PAYG withheld and PAYG instalment</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
+      <c r="B46" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2677,17 +2686,17 @@
           <t>Interest and equipment finance</t>
         </is>
       </c>
-      <c r="B47" s="14" t="n">
+      <c r="B47" s="15" t="n">
         <v>-6080</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <f>B41+B42+B43+B44+B45+B46+B47</f>
         <v/>
       </c>
@@ -2702,34 +2711,34 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Unpaid invoices collected in October</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Each invoice unpaid at the start, on its customer's usual payment date (next banking day)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Expected in the month (incl. GST)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>185678</v>
       </c>
     </row>
@@ -2743,34 +2752,34 @@
     <row r="57"/>
     <row r="58"/>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>New work collected in October</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Contract fees (1st of the month, on each contract's terms) + installations and call-outs at the last three months' run rate</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr"/>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>Expected in the month (incl. GST)</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n">
+      <c r="B62" s="17" t="n">
         <v>26600</v>
       </c>
     </row>
@@ -2784,22 +2793,22 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>Pay runs in October</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>Number of fortnightly pay runs × the cash each one takes</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr"/>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
@@ -2811,7 +2820,7 @@
           <t>Last pay run, net pay + super (17 September)</t>
         </is>
       </c>
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="15" t="n">
         <v>36611</v>
       </c>
     </row>
@@ -2821,17 +2830,17 @@
           <t>Pay runs in October (1 Oct, 15 Oct, 29 Oct)</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n">
+      <c r="B70" s="15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>Paid to employees and their super funds in October</t>
         </is>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="17">
         <f>B69*B70</f>
         <v/>
       </c>
@@ -2846,22 +2855,22 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>Suppliers and overheads in October</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Last month's bills (trade creditors) + the month's overheads, half on the 15th and half at month end, on banking days</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
@@ -2873,7 +2882,7 @@
           <t>September's bills for materials and subcontractors, incl. GST</t>
         </is>
       </c>
-      <c r="B78" s="14" t="n">
+      <c r="B78" s="15" t="n">
         <v>85866</v>
       </c>
     </row>
@@ -2883,7 +2892,7 @@
           <t>Overheads, incl. GST (at September's level)</t>
         </is>
       </c>
-      <c r="B79" s="14" t="n">
+      <c r="B79" s="15" t="n">
         <v>35310</v>
       </c>
     </row>
@@ -2893,7 +2902,7 @@
           <t>October's supplier bills</t>
         </is>
       </c>
-      <c r="B80" s="14">
+      <c r="B80" s="15">
         <f>B78+B79</f>
         <v/>
       </c>
@@ -2904,7 +2913,7 @@
           <t>October run due 15 October: paid in October</t>
         </is>
       </c>
-      <c r="B81" s="14" t="n">
+      <c r="B81" s="15" t="n">
         <v>-60588</v>
       </c>
     </row>
@@ -2914,17 +2923,17 @@
           <t>October run due 31 October, lands Mon 2 Nov (31 Oct isn't a banking day): paid in November, not October</t>
         </is>
       </c>
-      <c r="B82" s="14" t="n">
+      <c r="B82" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="15" t="inlineStr">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t>Paid in October</t>
         </is>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="17">
         <f>B81+B82</f>
         <v/>
       </c>
@@ -2932,22 +2941,22 @@
     <row r="84"/>
     <row r="85"/>
     <row r="86">
-      <c r="A86" s="13" t="inlineStr">
+      <c r="A86" s="14" t="inlineStr">
         <is>
           <t>BAS in October</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>GST on sales − GST credits + PAYG withheld + PAYG instalment, for the quarter, due on the 28th (quarterly, self-lodged)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr"/>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
@@ -2959,7 +2968,7 @@
           <t>GST on sales less GST credits, July to September</t>
         </is>
       </c>
-      <c r="B89" s="14" t="n">
+      <c r="B89" s="15" t="n">
         <v>-32817</v>
       </c>
     </row>
@@ -2969,7 +2978,7 @@
           <t>PAYG withheld from pay runs, July to September</t>
         </is>
       </c>
-      <c r="B90" s="14" t="n">
+      <c r="B90" s="15" t="n">
         <v>-47754</v>
       </c>
     </row>
@@ -2979,17 +2988,17 @@
           <t>PAYG income tax instalment, July to September</t>
         </is>
       </c>
-      <c r="B91" s="14" t="n">
+      <c r="B91" s="15" t="n">
         <v>-5682</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="inlineStr">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>BAS paid in October</t>
         </is>
       </c>
-      <c r="B92" s="16">
+      <c r="B92" s="17">
         <f>B89+B90+B91</f>
         <v/>
       </c>
@@ -3004,34 +3013,34 @@
     <row r="94"/>
     <row r="95"/>
     <row r="96">
-      <c r="A96" s="13" t="inlineStr">
+      <c r="A96" s="14" t="inlineStr">
         <is>
           <t>Interest and equipment finance in October</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>Interest at month end + the equipment finance repayment on the 28th (no GST on either)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr"/>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr"/>
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Paid in the month</t>
         </is>
       </c>
-      <c r="B99" s="16" t="n">
+      <c r="B99" s="17" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -3044,7 +3053,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3091,1946 +3100,1946 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Actual or forecast</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Money in</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Money out</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
         <v>48440</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>132057</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
         <v>1344</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="n">
+      <c r="D7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>133401</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="n">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>133401</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14" t="n">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>133401</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14" t="n">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>133401</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
         <v>60769</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14" t="n">
+      <c r="D11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>194170</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
         <v>8734</v>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14" t="n">
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>202904</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14" t="n">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="n">
         <v>202904</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
         <v>22880</v>
       </c>
-      <c r="D14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="14" t="n">
+      <c r="D14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="n">
         <v>225784</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="14" t="n">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>225784</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14" t="n">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>225784</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
         <v>4694</v>
       </c>
-      <c r="D17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="14" t="n">
+      <c r="D17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15" t="n">
         <v>230478</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="14" t="n">
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>232043</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14" t="n">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>232043</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14" t="n">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>-97199</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <v>134844</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="14" t="n">
+      <c r="D21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
         <v>136409</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="14" t="n">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
         <v>136409</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="14" t="n">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="n">
         <v>136409</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
         <v>20534</v>
       </c>
-      <c r="D24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="14" t="n">
+      <c r="D24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="15" t="n">
         <v>156943</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="14" t="n">
+      <c r="D25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="15" t="n">
         <v>158508</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="14" t="n">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="15" t="n">
         <v>158508</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="14" t="n">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="15" t="n">
         <v>158508</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>13664</v>
       </c>
-      <c r="D28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="14" t="n">
+      <c r="D28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>172172</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="14" t="n">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="15" t="n">
         <v>172172</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="14" t="n">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="n">
         <v>172172</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
         <v>4694</v>
       </c>
-      <c r="D31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="14" t="n">
+      <c r="D31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="15" t="n">
         <v>176866</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="14" t="n">
+      <c r="D32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="15" t="n">
         <v>178431</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="14" t="n">
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="n">
         <v>-91253</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="15" t="n">
         <v>87178</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
         <v>18700</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="15" t="n">
         <v>69267</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="14" t="n">
+      <c r="D35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="15" t="n">
         <v>70832</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="14" t="n">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="15" t="n">
         <v>70832</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="14" t="n">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <v>70832</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
         <v>68527</v>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="15" t="n">
         <v>-61668</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="E38" s="15" t="n">
         <v>77691</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="14" t="n">
+      <c r="D39" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="15" t="n">
         <v>79256</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="14" t="n">
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="15" t="n">
         <v>79256</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="14" t="n">
+      <c r="D41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="15" t="n">
         <v>86230</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D42" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="14" t="n">
+      <c r="D42" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="15" t="n">
         <v>94768</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>2026-11-07</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="14" t="n">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="15" t="n">
         <v>94768</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="14" t="n">
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
         <v>94768</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n">
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="14" t="n">
+      <c r="D45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="15" t="n">
         <v>113410</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D46" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="14" t="n">
+      <c r="D46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="15" t="n">
         <v>114975</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D47" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="14" t="n">
+      <c r="D47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="15" t="n">
         <v>121949</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n">
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D48" s="14" t="n">
+      <c r="D48" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E48" s="14" t="n">
+      <c r="E48" s="15" t="n">
         <v>92312</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D49" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="14" t="n">
+      <c r="D49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="15" t="n">
         <v>100851</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>2026-11-14</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="14" t="n">
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="15" t="n">
         <v>100851</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="14" t="n">
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="15" t="n">
         <v>100851</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n">
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D52" s="14" t="n">
+      <c r="D52" s="15" t="n">
         <v>-60588</v>
       </c>
-      <c r="E52" s="14" t="n">
+      <c r="E52" s="15" t="n">
         <v>58905</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n">
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="14" t="n">
+      <c r="D53" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="15" t="n">
         <v>60469</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D54" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="14" t="n">
+      <c r="D54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="15" t="n">
         <v>67443</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D55" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="14" t="n">
+      <c r="D55" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="15" t="n">
         <v>74417</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D56" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="14" t="n">
+      <c r="D56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="15" t="n">
         <v>82956</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="14" t="n">
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="15" t="n">
         <v>82956</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>2026-11-22</t>
         </is>
       </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="14" t="n">
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15" t="n">
         <v>82956</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="14" t="n">
+      <c r="D59" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="15" t="n">
         <v>101598</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="inlineStr">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D60" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="14" t="n">
+      <c r="D60" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="15" t="n">
         <v>103163</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D61" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="14" t="n">
+      <c r="D61" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="15" t="n">
         <v>110137</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D62" s="14" t="n">
+      <c r="D62" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E62" s="14" t="n">
+      <c r="E62" s="15" t="n">
         <v>80500</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D63" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="14" t="n">
+      <c r="D63" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="15" t="n">
         <v>89039</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="14" t="n">
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15" t="n">
         <v>89039</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="14" t="n">
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="15" t="n">
         <v>89039</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D66" s="14" t="n">
+      <c r="D66" s="15" t="n">
         <v>-66668</v>
       </c>
-      <c r="E66" s="14" t="n">
+      <c r="E66" s="15" t="n">
         <v>41013</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" s="18" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
       </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="n">
         <v>51449</v>
       </c>
-      <c r="D67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="14" t="n">
+      <c r="D67" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="15" t="n">
         <v>92462</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="14" t="n">
+      <c r="D68" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="15" t="n">
         <v>99436</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>2026-12-03</t>
         </is>
       </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="n">
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D69" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="14" t="n">
+      <c r="D69" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="15" t="n">
         <v>106410</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n">
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D70" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="14" t="n">
+      <c r="D70" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="15" t="n">
         <v>114949</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="17" t="inlineStr">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="14" t="n">
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="15" t="n">
         <v>114949</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>2026-12-06</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="14" t="n">
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="15" t="n">
         <v>114949</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="A73" s="18" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="n">
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="14" t="n">
+      <c r="D73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="15" t="n">
         <v>133591</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>2026-12-08</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="n">
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D74" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="14" t="n">
+      <c r="D74" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="15" t="n">
         <v>135156</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="inlineStr">
+      <c r="A75" s="18" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="n">
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D75" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="14" t="n">
+      <c r="D75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="15" t="n">
         <v>142130</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="n">
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D76" s="14" t="n">
+      <c r="D76" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E76" s="14" t="n">
+      <c r="E76" s="15" t="n">
         <v>112493</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="n">
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="14" t="n">
+      <c r="D77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="15" t="n">
         <v>121032</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="17" t="inlineStr">
+      <c r="A78" s="18" t="inlineStr">
         <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="14" t="n">
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="15" t="n">
         <v>121032</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="A79" s="18" t="inlineStr">
         <is>
           <t>2026-12-13</t>
         </is>
       </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="14" t="n">
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="15" t="n">
         <v>121032</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="inlineStr">
+      <c r="A80" s="18" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="n">
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D80" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="14" t="n">
+      <c r="D80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="15" t="n">
         <v>139674</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="A81" s="18" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="n">
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D81" s="14" t="n">
+      <c r="D81" s="15" t="n">
         <v>-60588</v>
       </c>
-      <c r="E81" s="14" t="n">
+      <c r="E81" s="15" t="n">
         <v>80650</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="17" t="inlineStr">
+      <c r="A82" s="18" t="inlineStr">
         <is>
           <t>2026-12-16</t>
         </is>
       </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="n">
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D82" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="14" t="n">
+      <c r="D82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="15" t="n">
         <v>87624</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="A83" s="18" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="n">
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D83" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="14" t="n">
+      <c r="D83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="15" t="n">
         <v>94598</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="17" t="inlineStr">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>2026-12-18</t>
         </is>
       </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="n">
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D84" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="14" t="n">
+      <c r="D84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="15" t="n">
         <v>103137</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="17" t="inlineStr">
+      <c r="A85" s="18" t="inlineStr">
         <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="14" t="n">
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="15" t="n">
         <v>103137</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="inlineStr">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="14" t="n">
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="15" t="n">
         <v>103137</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="17" t="inlineStr">
+      <c r="A87" s="18" t="inlineStr">
         <is>
           <t>2026-12-21</t>
         </is>
       </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="n">
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="n">
         <v>18642</v>
       </c>
-      <c r="D87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="14" t="n">
+      <c r="D87" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="15" t="n">
         <v>121779</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="17" t="inlineStr">
+      <c r="A88" s="18" t="inlineStr">
         <is>
           <t>2026-12-22</t>
         </is>
       </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="n">
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D88" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="14" t="n">
+      <c r="D88" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="15" t="n">
         <v>123344</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n">
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="14" t="n">
+      <c r="D89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="15" t="n">
         <v>130318</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="17" t="inlineStr">
+      <c r="A90" s="18" t="inlineStr">
         <is>
           <t>2026-12-24</t>
         </is>
       </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="n">
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D90" s="14" t="n">
+      <c r="D90" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E90" s="14" t="n">
+      <c r="E90" s="15" t="n">
         <v>100681</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>2026-12-25</t>
         </is>
       </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="14" t="n">
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="15" t="n">
         <v>100681</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="17" t="inlineStr">
+      <c r="A92" s="18" t="inlineStr">
         <is>
           <t>2026-12-26</t>
         </is>
       </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="14" t="n">
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="15" t="n">
         <v>100681</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="17" t="inlineStr">
+      <c r="A93" s="18" t="inlineStr">
         <is>
           <t>2026-12-27</t>
         </is>
       </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="14" t="n">
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="15" t="n">
         <v>100681</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+      <c r="A94" s="18" t="inlineStr">
         <is>
           <t>2026-12-28</t>
         </is>
       </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="14" t="n">
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15" t="n">
         <v>100681</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="A95" s="18" t="inlineStr">
         <is>
           <t>2026-12-29</t>
         </is>
       </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="n">
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="n">
         <v>27181</v>
       </c>
-      <c r="D95" s="14" t="n">
+      <c r="D95" s="15" t="n">
         <v>-5000</v>
       </c>
-      <c r="E95" s="14" t="n">
+      <c r="E95" s="15" t="n">
         <v>122862</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="17" t="inlineStr">
+      <c r="A96" s="18" t="inlineStr">
         <is>
           <t>2026-12-30</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C96" s="14" t="n">
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="n">
         <v>6974</v>
       </c>
-      <c r="D96" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="14" t="n">
+      <c r="D96" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="15" t="n">
         <v>129836</v>
       </c>
     </row>
@@ -5040,7 +5049,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
